--- a/data/modelling/atribucion/celulares/df_attr_values_sent.xlsx
+++ b/data/modelling/atribucion/celulares/df_attr_values_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D468"/>
+  <dimension ref="A1:D474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53650</v>
+        <v>48249</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7392052513531429</v>
+        <v>0.8018716034097926</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63249</v>
+        <v>65599.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -476,15 +476,15 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6263365885580997</v>
+        <v>0.1124530004578732</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>44049</v>
+        <v>57775</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -492,15 +492,15 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7169482794073005</v>
+        <v>0.2369482547516044</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128449.5</v>
+        <v>120449.5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -508,15 +508,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.448891785580965</v>
+        <v>-1.848437497637431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>294995</v>
+        <v>74734.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -524,15 +524,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.574636829582855</v>
+        <v>-0.9742356228418264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73425</v>
+        <v>25549</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2616989195132922</v>
+        <v>1.2173828598389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28499</v>
+        <v>84949.5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>313</v>
+        <v>119</v>
       </c>
       <c r="D8" t="n">
-        <v>1.087689085694642</v>
+        <v>-0.2977934767316481</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84617.5</v>
+        <v>33499</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -572,15 +572,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03669718864069189</v>
+        <v>1.342856805844724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98406</v>
+        <v>163202</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -588,15 +588,15 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3487419225718288</v>
+        <v>-1.576246051909314</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>36999</v>
+        <v>39764</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -604,15 +604,15 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>1.024099074206151</v>
+        <v>0.9120976053032147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>187598</v>
+        <v>4049.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -620,15 +620,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.056491239499283</v>
+        <v>-0.02328533723915003</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4299</v>
+        <v>97182</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -636,15 +636,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>0.351347624946997</v>
+        <v>-0.7004907902230539</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20499.5</v>
+        <v>18298.5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -652,15 +652,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9272607261349877</v>
+        <v>0.8584274555739156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13149</v>
+        <v>11799.5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -668,32 +668,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8856480951855359</v>
+        <v>-0.06154880859759897</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>398999</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>658</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.631376840097939</v>
+        <v>0.8336592632497253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -702,16 +704,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>661</v>
+        <v>362</v>
       </c>
       <c r="D17" t="n">
-        <v>1.71327705166354</v>
+        <v>0.9824630261223265</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -720,16 +722,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>368</v>
+        <v>273</v>
       </c>
       <c r="D18" t="n">
-        <v>1.759860624664694</v>
+        <v>1.162863310432579</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Sansei</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -738,16 +740,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>274</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.967237599062774</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sansei</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.386159657200589</v>
+        <v>-0.6716168671879873</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Kodak</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4743517031262542</v>
+        <v>-0.7731270491353208</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kodak</t>
+          <t>ZTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3841695322605004</v>
+        <v>0.1998391549815973</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="D23" t="n">
-        <v>1.136206267150183</v>
+        <v>1.381764109728264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>Alcatel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="D24" t="n">
-        <v>2.177436461506667</v>
+        <v>1.019389127306514</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alcatel</t>
+          <t>Philco</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -846,16 +846,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.876880784640657</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Philco</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -864,16 +862,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.9049565446222756</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -882,16 +878,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3869394752294257</v>
+        <v>-1.583279243384249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -900,16 +896,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2845522064921456</v>
+        <v>1.168809522290517</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Ulefone</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -918,16 +914,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>125</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.95816680700302</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ulefone</t>
+          <t>Blackview</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -936,16 +930,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-0.7560332079334553</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Blackview</t>
+          <t>BLU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -954,16 +946,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6981024304266435</v>
+        <v>-0.7138790974140234</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BLU</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -972,16 +964,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4431340796306594</v>
+        <v>-0.6081753830513436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iPro</t>
+          <t>Energizer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -990,16 +982,14 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.52032514072131</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Energizer</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1008,16 +998,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6797589957664102</v>
+        <v>-0.9826212073406835</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>BLU - IPRO - NOKIA - GENERICO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1026,16 +1016,14 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.2112473347671158</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Konka</t>
+          <t>RugGear</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1044,14 +1032,14 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BLU - IPRO - NOKIA - GENERICO</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1060,16 +1048,14 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.7012915209500825</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RugGear</t>
+          <t>Realme</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1080,14 +1066,12 @@
       <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="n">
-        <v>-0.8975215050356996</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1096,16 +1080,14 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.625485966168261</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Realme</t>
+          <t>Excess</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1114,16 +1096,14 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.8128532399942262</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>P&amp;S Mobile</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1132,16 +1112,14 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.7783234595547166</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Excess</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1150,16 +1128,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6998458032090459</v>
+        <v>-1.047001154394691</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P&amp;S Mobile</t>
+          <t>T-36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1168,16 +1146,14 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.676757786810921</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1186,16 +1162,14 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.1581063688592571</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T-36</t>
+          <t>BLU,IPRO, OTRAS MARCAS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1204,14 +1178,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>IPRO - BLU - EXC SEGUN STOCK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1220,16 +1194,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-0.2202575059033476</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BLU,IPRO, OTRAS MARCAS</t>
+          <t>Doogee</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1238,16 +1210,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.7000483242887573</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IPRO - BLU - EXC SEGUN STOCK</t>
+          <t>Panacom</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1256,16 +1226,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-0.5233769061380251</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>Noblex</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1274,16 +1242,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-0.8445234792520931</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Panacom</t>
+          <t>Luo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1292,16 +1258,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.7236297639382039</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noblex</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1310,16 +1274,14 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-0.8596384979901945</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Luo</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1328,14 +1290,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.3690875122032231</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1344,16 +1308,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.9390782010299169</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>BlackBerry</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1362,16 +1324,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>34</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.7176747965553565</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Logic</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1380,49 +1340,45 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.6204361080443687</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BlackBerry</t>
-        </is>
+      <c r="A56" t="n">
+        <v>161.29</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>270</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7785039656331846</v>
+        <v>0.5976843431288477</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
+      <c r="A57" t="n">
+        <v>164.211</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>288</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.5681523271260113</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>162.814</v>
+        <v>171.704</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1430,15 +1386,15 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="D58" t="n">
-        <v>1.434435212264634</v>
+        <v>-1.361235374047707</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>164.973</v>
+        <v>168.91</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1446,15 +1402,15 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1087736722079989</v>
+        <v>0.3283876872834682</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>171.45</v>
+        <v>165.989</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1462,15 +1418,15 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="D60" t="n">
-        <v>0.031707022158243</v>
+        <v>0.5043205951840385</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>167.64</v>
+        <v>156.464</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1478,15 +1434,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="D61" t="n">
-        <v>1.074878774988614</v>
+        <v>0.917861669676008</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>157.48</v>
+        <v>124.46</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1494,15 +1450,15 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8560898099650313</v>
+        <v>0.3883445720846415</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>46.60899999999999</v>
+        <v>146.05</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1510,15 +1466,15 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.259239872417823</v>
+        <v>-0.001276342317759906</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>104.14</v>
+        <v>152.2476</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1526,15 +1482,15 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9095185281114754</v>
+        <v>0.307406711760835</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>144.272</v>
+        <v>183.134</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1542,15 +1498,15 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.5863908292115726</v>
+        <v>-1.33182041437463</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>149.86</v>
+        <v>139.065</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1558,15 +1514,15 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D66" t="n">
-        <v>1.447869126731798</v>
+        <v>0.576912806300599</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>174.117</v>
+        <v>134.62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1574,15 +1530,15 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.050930518199917</v>
+        <v>1.530496955344908</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>63.5</v>
+        <v>107.95</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1590,15 +1546,15 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.5871772096788644</v>
+        <v>-1.888930882897237</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129.54</v>
+        <v>141.755</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1606,64 +1562,68 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>199</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.9864042909471411</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>140.87</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HD+</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6850357566722652</v>
+        <v>-0.06659521039710038</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>193.04</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Full HD+</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.373141748949873</v>
+        <v>1.406229745781011</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>136.525</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Quad HD+</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.6412476149502028</v>
+        <v>-0.4240809905204669</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HD+</t>
+          <t>FHD+</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1672,16 +1632,14 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>269</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.9544171061642429</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full HD+</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1690,16 +1648,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>389</v>
+        <v>22</v>
       </c>
       <c r="D74" t="n">
-        <v>2.186812117802392</v>
+        <v>-0.915553544863444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Quad HD+</t>
+          <t>FWVGA+</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1708,16 +1666,14 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.5459890836523178</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FHD+</t>
+          <t>QXGA+</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1726,16 +1682,14 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-0.004294579886084199</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>FWVGA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1744,16 +1698,14 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.07487271692249151</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FWVGA+</t>
+          <t>Full HD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1762,16 +1714,14 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-1.003525982677671</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QXGA+</t>
+          <t>QQVGA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1780,16 +1730,14 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-0.5070715837747362</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FWVGA</t>
+          <t>QHD+</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1805,7 +1753,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full HD</t>
+          <t>Edge Quad HD+</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1814,16 +1762,14 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-0.8787450217300857</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QQVGA</t>
+          <t>QHD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1832,16 +1778,14 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-0.8077188741808836</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QHD+</t>
+          <t>Quad HD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1850,48 +1794,50 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QHD</t>
+          <t>Super AMOLED</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
+          <t>Tecnología de la pantalla</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1.711989656563132</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Quad HD</t>
+          <t>PLS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
+          <t>Tecnología de la pantalla</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.5607349822919839</v>
+        <v>0.3472647063417971</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Super AMOLED</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1900,16 +1846,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>253</v>
+        <v>360</v>
       </c>
       <c r="D86" t="n">
-        <v>1.863614746691651</v>
+        <v>-0.1248272216098595</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1918,16 +1864,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6669553773059933</v>
+        <v>0.6580580750731616</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>HDR10+</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1936,16 +1882,14 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>375</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0.4106152886926056</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>Dynamic AMOLED 2X</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1954,16 +1898,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D89" t="n">
-        <v>1.097204986601692</v>
+        <v>-0.3797162401354914</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HDR10+</t>
+          <t>AMOLED</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1972,16 +1916,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.7110269877796596</v>
+        <v>0.4869955435720408</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dynamic AMOLED 2X</t>
+          <t>Dynamic AMOLED</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1990,16 +1934,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1894661060804911</v>
+        <v>0.1501774947513672</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2008,16 +1952,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9715819972829921</v>
+        <v>-1.292892870274404</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dynamic AMOLED</t>
+          <t>IPS LCD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2026,16 +1970,14 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>70</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.3762573632233178</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>PLS LCD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2044,16 +1986,14 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>50</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-0.612805286894309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IPS LCD</t>
+          <t>PLS TFT LCD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2062,16 +2002,14 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-1.236555629430969</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLS LCD</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2080,14 +2018,14 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLS TFT LCD</t>
+          <t>Super AMOLED Plus</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2096,14 +2034,14 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>LTPS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2112,52 +2050,52 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.263424776162883</v>
+        <v>-1.557049144281746</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Super AMOLED Plus</t>
+          <t>Infinity-U</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.029660950365611</v>
+        <v>-0.429090338045517</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LTPS</t>
+          <t>Infinity-V Display</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Tipo de pantalla</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.722222235245311</v>
+        <v>-0.04737906494250834</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Infinity-U</t>
+          <t>Max Vision</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2166,16 +2104,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.05331603353287916</v>
+        <v>0.480423841475649</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Infinity-V Display</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2184,16 +2122,14 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>60</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0.4000051203165483</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Max Vision</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2202,16 +2138,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>148</v>
+        <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>0.8731079548667333</v>
+        <v>0.3212310139274446</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Max Vision Display</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2220,14 +2156,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.338318673181439</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>DotDisplay</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2236,16 +2174,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D105" t="n">
-        <v>0.6429118082290862</v>
+        <v>1.18624199338902</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Max Vision Display</t>
+          <t>Dot Drop Display</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2254,16 +2192,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D106" t="n">
-        <v>0.2433280741530347</v>
+        <v>0.1814671823406594</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DotDisplay</t>
+          <t>Infinity-O Display</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2272,16 +2210,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D107" t="n">
-        <v>1.652341216179771</v>
+        <v>1.433388225046562</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dot Drop Display</t>
+          <t>Infinity Flex</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2290,16 +2228,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9878288670727058</v>
+        <v>-0.6244874458461909</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Infinity-O Display</t>
+          <t>Infinity-V</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2308,16 +2246,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="D109" t="n">
-        <v>1.715397920671777</v>
+        <v>-1.333593650940316</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Infinity Flex</t>
+          <t>Full Display</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2326,16 +2264,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.4293110281308573</v>
+        <v>-0.9358383220619259</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Infinity-V</t>
+          <t>V-Notch</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2344,16 +2282,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.8926102742570686</v>
+        <v>1.520394567560444</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Display</t>
+          <t>Vast Display</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2362,16 +2300,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.5235306346517947</v>
+        <v>-0.1873759036787893</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V-Notch</t>
+          <t>Liquid Retina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2380,16 +2318,14 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>24</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1.958745321486704</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Vast Display</t>
+          <t>Super Retina XDR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2398,16 +2334,14 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>26</v>
-      </c>
-      <c r="D114" t="n">
-        <v>-0.02018682217291671</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Liquid Retina</t>
+          <t>Super AMOLED</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2416,16 +2350,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.2027239596255518</v>
+        <v>0.7681106042409712</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Super Retina XDR</t>
+          <t>IPS LCD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2436,14 +2370,12 @@
       <c r="C116" t="n">
         <v>1</v>
       </c>
-      <c r="D116" t="n">
-        <v>-0.8650642241470134</v>
-      </c>
+      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Super AMOLED</t>
+          <t>Dynamic AMOLED 2X</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2452,16 +2384,14 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>17</v>
-      </c>
-      <c r="D117" t="n">
-        <v>1.057574155066672</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IPS LCD</t>
+          <t>V Notch Display</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2470,16 +2400,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.303280876257025</v>
+        <v>-1.471308737595449</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>V Notch Display</t>
+          <t>TFT LCD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2488,16 +2418,14 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-1.020396958332961</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TFT LCD</t>
+          <t>Retina HD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2506,16 +2434,14 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-0.4324927639136351</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Retina HD</t>
+          <t>Mini Notch Display</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2524,14 +2450,14 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Mini Notch Display</t>
+          <t>WaterDrop Screen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2540,16 +2466,14 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-1.084960261760648</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WaterDrop Screen</t>
+          <t>Infinity Flex Display</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2558,16 +2482,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.080492979593108</v>
+        <v>-0.847879575442084</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Infinity Flex Display</t>
+          <t>Largue Screen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2576,16 +2500,14 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-0.4427103718836294</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Largue Screen</t>
+          <t>Retina</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2594,16 +2516,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.6860056927954266</v>
+        <v>1.828474657920764</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Retina</t>
+          <t>RawColor display</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2612,16 +2534,14 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>54</v>
-      </c>
-      <c r="D126" t="n">
-        <v>1.932348437426649</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RawColor display</t>
+          <t>WaterDrop Full Screen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2630,14 +2550,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.2370331131274859</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WaterDrop Full Screen</t>
+          <t>Sun readable display</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2646,16 +2568,14 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0.1248950580852249</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sun readable display</t>
+          <t>FullView Display</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2698,9 +2618,7 @@
       <c r="C131" t="n">
         <v>2</v>
       </c>
-      <c r="D131" t="n">
-        <v>-1.078637645325841</v>
-      </c>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2717,7 +2635,7 @@
         <v>11</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.8312140701953321</v>
+        <v>-1.26742726103981</v>
       </c>
     </row>
     <row r="133">
@@ -2734,9 +2652,7 @@
       <c r="C133" t="n">
         <v>2</v>
       </c>
-      <c r="D133" t="n">
-        <v>-0.6415493369792178</v>
-      </c>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2773,7 +2689,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ultra Smooth Display</t>
+          <t>Waterdrop Screen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2789,7 +2705,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TFT</t>
+          <t>Ultra Smooth Display</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2805,7 +2721,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMOLED</t>
+          <t>TFT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2821,54 +2737,54 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Always-on Display</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tipo de pantalla</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>CinemaVision Display</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Tipo de pantalla</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>277.5</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Píxeles por pulgada de la pantalla</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>140</v>
-      </c>
-      <c r="D140" t="n">
-        <v>0.3453906560814913</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>397</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Píxeles por pulgada de la pantalla</t>
-        </is>
-      </c>
       <c r="C141" t="n">
-        <v>98</v>
-      </c>
-      <c r="D141" t="n">
-        <v>0.73151827272646</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>383.5</v>
+        <v>278</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -2876,15 +2792,15 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D142" t="n">
-        <v>1.083259089090946</v>
+        <v>0.6179114017562232</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>264</v>
+        <v>264.5</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -2892,15 +2808,15 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3158511429613673</v>
+        <v>-0.1589073091287692</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>405.5</v>
+        <v>398</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -2908,15 +2824,15 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="D144" t="n">
-        <v>1.407785114909527</v>
+        <v>0.8255865052338475</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>424.5</v>
+        <v>384.5</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -2924,15 +2840,15 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3664826741737165</v>
+        <v>0.5144085630128481</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>341.5</v>
+        <v>406</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -2940,15 +2856,15 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.2841009545786203</v>
+        <v>1.37735100089949</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>469.5</v>
+        <v>426</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -2956,15 +2872,15 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.5850278867922478</v>
+        <v>0.08647706062169105</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>293.5</v>
+        <v>342.5</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -2972,15 +2888,15 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3249032431008322</v>
+        <v>-0.386843205049896</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>227</v>
+        <v>478.5</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -2988,15 +2904,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>36</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-1.170688221580332</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>161</v>
+        <v>293.5</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3004,15 +2918,15 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.075595904897668</v>
+        <v>-0.1032428709921805</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>100.5</v>
+        <v>227</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -3020,15 +2934,15 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.326541939666303</v>
+        <v>-1.603190031398248</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>516.5</v>
+        <v>161</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3036,15 +2950,15 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.5909784849411828</v>
+        <v>-1.59332833660908</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>550.5</v>
+        <v>100.5</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3052,15 +2966,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>50</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1.759642903001396</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>577</v>
+        <v>516.5</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3068,31 +2980,31 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.301899703589382</v>
+        <v>-0.8797012549537774</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4770</v>
+        <v>551</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Capacidad de la batería</t>
+          <t>Píxeles por pulgada de la pantalla</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>375</v>
+        <v>52</v>
       </c>
       <c r="D155" t="n">
-        <v>1.526682880126802</v>
+        <v>1.303478476607853</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>4350</v>
+        <v>5250</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3100,15 +3012,15 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>161</v>
+        <v>383</v>
       </c>
       <c r="D156" t="n">
-        <v>1.14492370263359</v>
+        <v>1.303049797920718</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>412</v>
+        <v>4600</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -3116,15 +3028,15 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.8591506492640862</v>
+        <v>1.071158307920391</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>3287</v>
+        <v>4150</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -3132,15 +3044,15 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2299439093601888</v>
+        <v>1.171108277630791</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3600</v>
+        <v>457</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3148,15 +3060,15 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.2857624462756888</v>
+        <v>-1.132471994303715</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1910.5</v>
+        <v>3345</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -3164,15 +3076,15 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.960853259784954</v>
+        <v>-0.1153380554271396</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2675</v>
+        <v>3784.5</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3180,15 +3092,15 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.2474381244470742</v>
+        <v>-0.6139813609733935</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>3950</v>
+        <v>1660.5</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3196,15 +3108,15 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="D162" t="n">
-        <v>1.493017557259837</v>
+        <v>-1.160845052100384</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>3026</v>
+        <v>2714</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3212,15 +3124,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>245</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0.5194718589039942</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1625</v>
+        <v>3087</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -3228,15 +3138,15 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="D164" t="n">
-        <v>-1.139337626359778</v>
+        <v>0.2418718814723667</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2337.5</v>
+        <v>1987.5</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3244,15 +3154,15 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.7645945122349407</v>
+        <v>-1.210963870112741</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1155</v>
+        <v>2400</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3260,15 +3170,15 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.8505719371581524</v>
+        <v>-0.5312073490715988</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>5870</v>
+        <v>1200</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3276,15 +3186,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>44</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1.187104117047639</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2842.5</v>
+        <v>6090</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3292,34 +3200,30 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.9934354698073762</v>
+        <v>0.9776194170447051</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Polímero de litio</t>
-        </is>
+      <c r="A169" t="n">
+        <v>2871</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tipo de batería</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>764</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1.0647814431044</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ion de litio</t>
+          <t>Polímero de litio</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3328,16 +3232,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>584</v>
+        <v>762</v>
       </c>
       <c r="D170" t="n">
-        <v>0.6393622823178098</v>
+        <v>0.7071067811865476</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LiPo</t>
+          <t>Ion de litio</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3346,49 +3250,47 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>582</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.9040498961576015</v>
+        <v>-0.7071067811865476</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>LiPo</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Tipo de batería</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>5</v>
+      </c>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>Li-ion</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Tipo de batería</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="C173" t="n">
         <v>13</v>
       </c>
-      <c r="D172" t="n">
-        <v>-0.8000938292646079</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>1</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Con carga rápida</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>773</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.7071067811865474</v>
-      </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -3396,31 +3298,31 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>742</v>
+        <v>771</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.7071067811865479</v>
+        <v>0.7071067811865475</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Con carga rápida</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>77</v>
+        <v>740</v>
       </c>
       <c r="D175" t="n">
-        <v>0.6069478738966276</v>
+        <v>-0.7071067811865475</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.212</v>
+        <v>0.18</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -3428,15 +3330,15 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="D176" t="n">
-        <v>-1.804296558892799</v>
+        <v>0.5623598297297769</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.192</v>
+        <v>0.22</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3444,15 +3346,15 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3943201442087</v>
+        <v>-1.598542396279918</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.176</v>
+        <v>0.2</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3460,15 +3362,15 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4016502685438774</v>
+        <v>-0.08622060327823247</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.1615</v>
+        <v>0.16</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3476,15 +3378,15 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="D179" t="n">
-        <v>1.069852127422446</v>
+        <v>1.008730124176427</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.1985</v>
+        <v>0.15</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3492,15 +3394,15 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.4834438185443051</v>
+        <v>0.7974384377227033</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.169</v>
+        <v>0.14</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3508,15 +3410,15 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D181" t="n">
-        <v>0.6534366539666665</v>
+        <v>-0.6837653920707562</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.205</v>
+        <v>0.11</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -3524,15 +3426,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>30</v>
-      </c>
-      <c r="D182" t="n">
-        <v>-0.9194867341390132</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.1475</v>
+        <v>0.24</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -3540,15 +3440,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>81</v>
-      </c>
-      <c r="D183" t="n">
-        <v>1.009324374232734</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0.154</v>
+        <v>0.12</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -3556,79 +3454,77 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>77</v>
-      </c>
-      <c r="D184" t="n">
-        <v>1.167773770352736</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.139</v>
+        <v>128</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>41</v>
+        <v>357</v>
       </c>
       <c r="D185" t="n">
-        <v>0.04834201237199544</v>
+        <v>0.6903942733273427</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.116</v>
+        <v>256</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D186" t="n">
-        <v>0.5706899347594356</v>
+        <v>0.9829789219686452</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.2585</v>
+        <v>32</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="D187" t="n">
-        <v>-1.435700934233365</v>
+        <v>0.5937944946744781</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.223</v>
+        <v>64</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>49</v>
+        <v>187</v>
       </c>
       <c r="D188" t="n">
-        <v>-1.279409113945735</v>
+        <v>0.5915102063068071</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128</v>
+        <v>0.0029296875</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -3636,15 +3532,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>322</v>
-      </c>
-      <c r="D189" t="n">
-        <v>1.386959515669696</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>256</v>
+        <v>16</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -3652,15 +3546,15 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="D190" t="n">
-        <v>1.417039312650416</v>
+        <v>-0.1138800941311668</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>32</v>
+        <v>0.5</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -3668,15 +3562,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>235</v>
-      </c>
-      <c r="D191" t="n">
-        <v>1.36649548916901</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>64</v>
+        <v>0.0078125</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -3684,15 +3576,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>174</v>
-      </c>
-      <c r="D192" t="n">
-        <v>1.349709853602317</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.0029296875</v>
+        <v>6</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3700,15 +3590,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-0.773178801648186</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>16</v>
+        <v>0.03125</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -3716,15 +3604,15 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="D194" t="n">
-        <v>0.7330362279877881</v>
+        <v>-1.179129921307859</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -3732,15 +3620,15 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.9921264974335926</v>
+        <v>-1.565667880838248</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.0078125</v>
+        <v>0.00390625</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -3748,15 +3636,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-0.7722641883909884</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -3770,7 +3656,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.03125</v>
+        <v>4</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -3778,15 +3664,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>20</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-0.1341452810161013</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>8</v>
+        <v>0.048828125</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -3794,15 +3678,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>64</v>
-      </c>
-      <c r="D199" t="n">
-        <v>-0.5443775153435916</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.00390625</v>
+        <v>0.0234375</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -3812,13 +3694,11 @@
       <c r="C200" t="n">
         <v>4</v>
       </c>
-      <c r="D200" t="n">
-        <v>-0.6540776489032388</v>
-      </c>
+      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -3826,13 +3706,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>4</v>
+        <v>0.0009765625</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -3840,15 +3720,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-0.885164982625948</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0.048828125</v>
+        <v>0.0625</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -3862,67 +3740,71 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.0234375</v>
+        <v>4</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
+          <t>Memoria RAM</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>747</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.6597202616281812</v>
+        <v>0.05929140966137023</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.125</v>
+        <v>6</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
+          <t>Memoria RAM</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>354</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.8381852220894001</v>
+        <v>0.5294606878125119</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.0009765625</v>
+        <v>12</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
+          <t>Memoria RAM</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0</v>
-      </c>
-      <c r="D206" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.6826838715536577</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.0625</v>
+        <v>2</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
+          <t>Memoria RAM</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
-      </c>
-      <c r="D207" t="inlineStr"/>
+        <v>484</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-0.6900708653744029</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -3930,15 +3812,15 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>737</v>
+        <v>169</v>
       </c>
       <c r="D208" t="n">
-        <v>0.9200379473083494</v>
+        <v>0.7059603132541631</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -3946,15 +3828,15 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="D209" t="n">
-        <v>1.146385844075555</v>
+        <v>0.6691429726518411</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>12</v>
+        <v>0.00390625</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -3962,15 +3844,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>99</v>
-      </c>
-      <c r="D210" t="n">
-        <v>1.373013308500812</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -3978,15 +3858,15 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>475</v>
+        <v>247</v>
       </c>
       <c r="D211" t="n">
-        <v>0.331839175788438</v>
+        <v>-1.956468389559142</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -3994,15 +3874,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>169</v>
-      </c>
-      <c r="D212" t="n">
-        <v>1.435423847166163</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3</v>
+        <v>0.0078125</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -4010,15 +3888,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>328</v>
-      </c>
-      <c r="D213" t="n">
-        <v>1.226882819292726</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0.00390625</v>
+        <v>0.03125</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -4026,15 +3902,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
-      </c>
-      <c r="D214" t="n">
-        <v>-0.8837141428182554</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1</v>
+        <v>0.0234375</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4042,15 +3916,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>243</v>
-      </c>
-      <c r="D215" t="n">
-        <v>-0.6074331274887332</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4058,15 +3930,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
-      </c>
-      <c r="D216" t="n">
-        <v>-0.8963500081120193</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0.0078125</v>
+        <v>0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4074,15 +3944,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
-      </c>
-      <c r="D217" t="n">
-        <v>-0.8744455882293605</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0.03125</v>
+        <v>0.00048828125</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4090,15 +3958,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>21</v>
-      </c>
-      <c r="D218" t="n">
-        <v>-0.7997223964949756</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0.0234375</v>
+        <v>0.0625</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4108,13 +3974,11 @@
       <c r="C219" t="n">
         <v>3</v>
       </c>
-      <c r="D219" t="n">
-        <v>-0.8729136925895719</v>
-      </c>
+      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>0.0009765625</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -4128,7 +3992,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0.00048828125</v>
+        <v>1.5</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4136,13 +4000,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0.0625</v>
+        <v>0.75</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4150,59 +4014,61 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4</v>
-      </c>
-      <c r="D222" t="n">
-        <v>-0.8823534113860427</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0.0009765625</v>
+        <v>47.24</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
+          <t>Resolución de la cámara trasera principal</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0</v>
-      </c>
-      <c r="D223" t="inlineStr"/>
+        <v>371</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.4698818726997194</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1.5</v>
+        <v>62.48</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
+          <t>Resolución de la cámara trasera principal</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.6166505750130864</v>
+        <v>0.516458942771306</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.75</v>
+        <v>13.72</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
+          <t>Resolución de la cámara trasera principal</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" t="inlineStr"/>
+        <v>508</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-0.2341221630909988</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>48.9</v>
+        <v>50.28</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4210,15 +4076,15 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="D226" t="n">
-        <v>0.8658217722375279</v>
+        <v>-1.232680242247378</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>64.31999999999999</v>
+        <v>19.81</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -4226,15 +4092,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>248</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.9327398300075038</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>105.43</v>
+        <v>10.66</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -4242,15 +4106,15 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.09498058340254599</v>
+        <v>0.9888367740914761</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>12.93</v>
+        <v>1.52</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -4258,15 +4122,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>807</v>
-      </c>
-      <c r="D229" t="n">
-        <v>0.732415794024651</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>18.07</v>
+        <v>4.57</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -4274,15 +4136,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>247</v>
-      </c>
-      <c r="D230" t="n">
-        <v>1.566389338651189</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2.65</v>
+        <v>7.62</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -4290,15 +4150,15 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="D231" t="n">
-        <v>-1.059470035525112</v>
+        <v>-0.6596384380773139</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>7.79</v>
+        <v>16.76</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4306,15 +4166,15 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.1176530598101141</v>
+        <v>1.401113821921014</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>23.21</v>
+        <v>25.9</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4322,15 +4182,15 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.3342077458240367</v>
+        <v>-1.249850568067824</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>33.48</v>
+        <v>32</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -4340,13 +4200,11 @@
       <c r="C234" t="n">
         <v>35</v>
       </c>
-      <c r="D234" t="n">
-        <v>-1.121779512212471</v>
-      </c>
+      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>38.62</v>
+        <v>22.85</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4354,34 +4212,28 @@
         </is>
       </c>
       <c r="C235" t="n">
+        <v>22</v>
+      </c>
+      <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Resolución de la cámara trasera principal</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
         <v>1</v>
       </c>
-      <c r="D235" t="n">
-        <v>-1.369275798146591</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>1920 px x 1080 px</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Resolución de video de la cámara trasera</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>1140</v>
-      </c>
-      <c r="D236" t="n">
-        <v>1.950039762275108</v>
-      </c>
+      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4390,16 +4242,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>841</v>
+        <v>1120</v>
       </c>
       <c r="D237" t="n">
-        <v>2.729289036928854</v>
+        <v>0.400191503794748</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>7680 px x 4320 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4408,16 +4260,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>115</v>
+        <v>833</v>
       </c>
       <c r="D238" t="n">
-        <v>1.257504866855117</v>
+        <v>1.062364247572395</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>8K/24fps, 4K/30/60fps, 1080p/30/60/240/960fps, gyro-EIS</t>
+          <t>7680 px x 4320 px</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4426,16 +4278,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="D239" t="n">
-        <v>0.131317855528787</v>
+        <v>-0.1648441625088148</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3840 px x 1080 px</t>
+          <t>8K/24fps, 4K/30/60fps, 1080p/30/60/240/960fps, gyro-EIS</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4444,14 +4296,14 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3840 px x 2460 px</t>
+          <t>3840 px x 1080 px</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4467,7 +4319,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2160 px x 3840 px</t>
+          <t>3840 px x 2460 px</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4476,16 +4328,14 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>5</v>
-      </c>
-      <c r="D242" t="n">
-        <v>-0.5235055928830659</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>2160 px x 3840 px</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4494,16 +4344,14 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>70</v>
-      </c>
-      <c r="D243" t="n">
-        <v>-0.0722767001190831</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>320 px x 240 px</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4512,16 +4360,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.6270960686184452</v>
+        <v>-1.297711588858328</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3840 x 2160</t>
+          <t>320 px x 240 px</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4530,16 +4378,14 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>22</v>
-      </c>
-      <c r="D245" t="n">
-        <v>-0.2228604239434098</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1080p a 30/60/240fps</t>
+          <t>3840 x 2160</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4548,16 +4394,14 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
-      </c>
-      <c r="D246" t="n">
-        <v>-0.6019132359768598</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1080 x 2400</t>
+          <t>1080p a 30/60/240fps</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4566,16 +4410,14 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
-      </c>
-      <c r="D247" t="n">
-        <v>-0.5353086333418293</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1080P@30FPS</t>
+          <t>1080 x 2400</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4584,16 +4426,14 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>11</v>
-      </c>
-      <c r="D248" t="n">
-        <v>-0.4220477838955038</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1920 x 1080</t>
+          <t>1080P@30FPS</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4602,14 +4442,14 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1080 px x 1920 px</t>
+          <t>1920 x 1080</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4618,16 +4458,14 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>7</v>
-      </c>
-      <c r="D250" t="n">
-        <v>-0.4279334931622065</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3840 px - 2160 px</t>
+          <t>1080 px x 1920 px</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4636,14 +4474,14 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1920 px - 1080 px</t>
+          <t>3840 px - 2160 px</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4652,16 +4490,14 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
-      </c>
-      <c r="D252" t="n">
-        <v>-0.5874235550891931</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2048 px x 1152 px</t>
+          <t>1920 px - 1080 px</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4670,16 +4506,14 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
-      </c>
-      <c r="D253" t="n">
-        <v>-0.4280834262499844</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>176 px x 144 px</t>
+          <t>2048 px x 1152 px</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4688,14 +4522,14 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5312 px x 2988 px</t>
+          <t>176 px x 144 px</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4704,16 +4538,14 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>10</v>
-      </c>
-      <c r="D255" t="n">
-        <v>-0.4422043175791388</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1440 px x 2960 px</t>
+          <t>5312 px x 2988 px</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4722,49 +4554,45 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
-      </c>
-      <c r="D256" t="n">
-        <v>-0.5756872284997556</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
+          <t>1440 px x 2960 px</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Resolución de video de la cámara trasera</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2</v>
+      </c>
+      <c r="D257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>640 px x 480 px</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="C257" t="n">
+      <c r="C258" t="n">
         <v>1</v>
       </c>
-      <c r="D257" t="n">
-        <v>-0.6018110622293904</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>13</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Resolución de la cámara frontal principal</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>225</v>
-      </c>
-      <c r="D258" t="n">
-        <v>1.193883170812546</v>
-      </c>
+      <c r="D258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -4772,15 +4600,15 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>460</v>
+        <v>221</v>
       </c>
       <c r="D259" t="n">
-        <v>0.5556918028451865</v>
+        <v>1.043385812701189</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -4788,15 +4616,15 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="D260" t="n">
-        <v>1.028531986775241</v>
+        <v>0.3647921400899965</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -4804,15 +4632,15 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="D261" t="n">
-        <v>0.7469328318800894</v>
+        <v>0.8737685954465978</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -4820,15 +4648,15 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>600</v>
+        <v>212</v>
       </c>
       <c r="D262" t="n">
-        <v>0.2663945083243074</v>
+        <v>0.5343083911936656</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -4836,15 +4664,15 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>88</v>
+        <v>590</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.1488940606734892</v>
+        <v>-0.0656745879457961</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -4852,15 +4680,15 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="D264" t="n">
-        <v>0.9966830908782958</v>
+        <v>-0.5936581552782438</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -4868,15 +4696,15 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="D265" t="n">
-        <v>0.955788743029292</v>
+        <v>0.8523687975844298</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -4884,15 +4712,15 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.6631759633793448</v>
+        <v>0.8435204042989509</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -4900,15 +4728,15 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D267" t="n">
-        <v>-1.292493486736976</v>
+        <v>-1.215950550343114</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -4916,15 +4744,15 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D268" t="n">
-        <v>-1.528448199282584</v>
+        <v>-2.018237548240018</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>25</v>
+        <v>0.08</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -4932,15 +4760,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>87</v>
-      </c>
-      <c r="D269" t="n">
-        <v>-0.167885422270003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -4948,13 +4774,15 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
-      </c>
-      <c r="D270" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.6186232995076597</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -4968,7 +4796,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -4976,15 +4804,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>5</v>
-      </c>
-      <c r="D272" t="n">
-        <v>-1.46073206544228</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -4992,50 +4818,42 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>23</v>
-      </c>
-      <c r="D273" t="n">
-        <v>-1.222286580998288</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Resolución de la cámara frontal principal</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>23</v>
+      </c>
+      <c r="D274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
         <v>24</v>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="C274" t="n">
-        <v>34</v>
-      </c>
-      <c r="D274" t="n">
-        <v>0.7400096442380073</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>1920 px x 1080 px</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Resolución de video de la cámara frontal</t>
-        </is>
-      </c>
       <c r="C275" t="n">
-        <v>1338</v>
-      </c>
-      <c r="D275" t="n">
-        <v>1.610597939695844</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>1920 px x 1080 px</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5044,16 +4862,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>293</v>
+        <v>1319</v>
       </c>
       <c r="D276" t="n">
-        <v>1.864565726851963</v>
+        <v>0.8680090475041817</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4K/30fps, 1080p/30/120fp</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5062,16 +4880,16 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.3707868602870479</v>
+        <v>1.246364638582715</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>4K/30fps, 1080p/30/120fp</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5080,16 +4898,14 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>201</v>
-      </c>
-      <c r="D278" t="n">
-        <v>0.6195982280965484</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4K a 30/60 fps, 1080p a 30 fp</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5098,14 +4914,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
-      </c>
-      <c r="D279" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.6200978519708343</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4K 30fps, 1080p 30fps</t>
+          <t>4K a 30/60 fps, 1080p a 30 fp</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5114,16 +4932,14 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>22</v>
-      </c>
-      <c r="D280" t="n">
-        <v>-0.6021439189655992</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1080p a 30fps</t>
+          <t>4K 30fps, 1080p 30fps</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -5132,16 +4948,14 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
-      </c>
-      <c r="D281" t="n">
-        <v>-0.8497495705786223</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1080p@30fps</t>
+          <t>1080p a 30fps</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5150,16 +4964,14 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
-      </c>
-      <c r="D282" t="n">
-        <v>-0.8062419760896046</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4K/30fps, 1080p/30/120fps</t>
+          <t>4K a 30/60 fps, 1080p a 30 fps</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5175,7 +4987,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>720 px x 1280 px</t>
+          <t>1080p@30fps</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5184,16 +4996,14 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
-      </c>
-      <c r="D284" t="n">
-        <v>-0.8270517211220292</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>0.001 Mpx</t>
+          <t>4K/30fps, 1080p/30/120fps</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5202,16 +5012,14 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>64</v>
-      </c>
-      <c r="D285" t="n">
-        <v>0.3128480389271424</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2560 px - 1440 px</t>
+          <t>720 px x 1280 px</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5220,14 +5028,14 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2560 px x 1440 px</t>
+          <t>0.001 Mpx</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5236,16 +5044,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="D287" t="n">
-        <v>0.7119176102456931</v>
+        <v>-1.057125014298378</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>640 px x 480 px</t>
+          <t>2560 px - 1440 px</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5254,16 +5062,14 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>4</v>
-      </c>
-      <c r="D288" t="n">
-        <v>-0.8107284223783706</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>720 px x 480 px</t>
+          <t>2560 px x 1440 px</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5272,52 +5078,48 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="D289" t="n">
-        <v>-0.8528250743959169</v>
+        <v>-0.4371508198176846</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MediaTek Helio G80</t>
+          <t>640 px x 480 px</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Modelo del procesador</t>
+          <t>Resolución de video de la cámara frontal</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>32</v>
-      </c>
-      <c r="D290" t="n">
-        <v>0.7629604469807243</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Exynos 850</t>
+          <t>720 px x 480 px</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Modelo del procesador</t>
+          <t>Resolución de video de la cámara frontal</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>22</v>
-      </c>
-      <c r="D291" t="n">
-        <v>-0.7665687665483966</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MediaTek MT6382 Helio G95</t>
+          <t>MediaTek Helio G80</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5326,16 +5128,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D292" t="n">
-        <v>1.211060667771811</v>
+        <v>0.5106930592363761</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MediaTek Helio G95</t>
+          <t>Exynos 850</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5344,16 +5146,16 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D293" t="n">
-        <v>0.221478754581882</v>
+        <v>-0.9020750522639338</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Snapdragon 870</t>
+          <t>MediaTek MT6382 Helio G95</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -5362,16 +5164,16 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D294" t="n">
-        <v>0.4991184718277501</v>
+        <v>0.9968461246063789</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Qualcomm® Snapdragon™ 870</t>
+          <t>MediaTek Helio G95</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5380,16 +5182,16 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D295" t="n">
-        <v>2.118997592757356</v>
+        <v>0.04868783089261638</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Qualcomm SM8450 Snapdragon 8 Gen 1 (4 nm)</t>
+          <t>Snapdragon 870</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5398,16 +5200,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D296" t="n">
-        <v>0.4523346148553126</v>
+        <v>0.4132320693791807</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 720</t>
+          <t>Qualcomm® Snapdragon™ 870</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5416,16 +5218,16 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D297" t="n">
-        <v>0.8283775239131276</v>
+        <v>2.163406615453173</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MediaTek MT6762G Helio G25</t>
+          <t>Qualcomm SM8450 Snapdragon 8 Gen 1 (4 nm)</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5434,16 +5236,16 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.9286089152543769</v>
+        <v>-0.07154034431247225</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Snapdragon 680</t>
+          <t>MediaTek Dimensity 720</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5452,16 +5254,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.824344497868773</v>
+        <v>0.5547090189481853</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Snapdragon 778G</t>
+          <t>MediaTek MT6762G Helio G25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5470,16 +5272,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D300" t="n">
-        <v>1.646136124377847</v>
+        <v>-1.067591452849831</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MediaTek Helio G25</t>
+          <t>Snapdragon 680</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5488,16 +5290,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D301" t="n">
-        <v>-1.466031128814704</v>
+        <v>-0.9760230629002722</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Exynos 2100</t>
+          <t>Snapdragon 778G</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5506,16 +5308,16 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D302" t="n">
-        <v>-0.1941381685365118</v>
+        <v>1.275006924330492</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Exynos 2100 Octa-Core</t>
+          <t>MediaTek Helio G25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5524,14 +5326,14 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Snapdragon 732G</t>
+          <t>Exynos 2100</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5540,16 +5342,16 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D304" t="n">
-        <v>0.2946916214788811</v>
+        <v>-0.6231303262873518</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Snapdragon 778G 5G</t>
+          <t>Exynos 2100 Octa-Core</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5558,16 +5360,14 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>21</v>
-      </c>
-      <c r="D305" t="n">
-        <v>1.44947513419724</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Snapdragon 695 5G</t>
+          <t>Snapdragon 732G</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5576,16 +5376,16 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D306" t="n">
-        <v>1.505099527255547</v>
+        <v>-0.006467734141439523</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Snapdragon 888</t>
+          <t>Snapdragon 778G 5G</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5594,16 +5394,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D307" t="n">
-        <v>-0.4606850894134716</v>
+        <v>1.239984231899858</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MediaTek Helio G85</t>
+          <t>Snapdragon 695 5G</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5612,16 +5412,16 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D308" t="n">
-        <v>1.187616943900951</v>
+        <v>1.485990349433809</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MediaTek MT6261M</t>
+          <t>Snapdragon 888</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5630,16 +5430,16 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D309" t="n">
-        <v>-1.323752161033089</v>
+        <v>-0.8228821769620804</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 1200-Ultra</t>
+          <t>MediaTek Helio G85</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5648,16 +5448,16 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D310" t="n">
-        <v>1.056509833074596</v>
+        <v>1.013891859775632</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Apple A13 Bionic</t>
+          <t>MediaTek MT6261M</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5666,16 +5466,14 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>31</v>
-      </c>
-      <c r="D311" t="n">
-        <v>1.979657384471867</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Apple A14 Bionic</t>
+          <t>MediaTek Dimensity 1200-Ultra</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5684,16 +5482,16 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.378815501728195</v>
+        <v>0.7927422981587411</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Spreadtrum SC9832E</t>
+          <t>Apple A13 Bionic</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5702,16 +5500,16 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D313" t="n">
-        <v>0.2956624005070917</v>
+        <v>1.713713910654977</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Snapdragon 888+ 5G</t>
+          <t>Apple A14 Bionic</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5720,16 +5518,16 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D314" t="n">
-        <v>2.232832159774346</v>
+        <v>-0.7133370071693288</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Snapdragon 460</t>
+          <t>Spreadtrum SC9832E</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5738,16 +5536,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D315" t="n">
-        <v>1.152738217401727</v>
+        <v>-0.005448867610861239</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MediaTek MTK6762D</t>
+          <t>Snapdragon 888+ 5G</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5756,16 +5554,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D316" t="n">
-        <v>0.9086834202597883</v>
+        <v>1.827230495843569</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>MediaTek MT6572</t>
+          <t>Snapdragon 460</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5774,16 +5572,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D317" t="n">
-        <v>-1.030236070895337</v>
+        <v>0.8805311156112003</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Apple A15 Bionic</t>
+          <t>MediaTek MTK6762D</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5792,16 +5590,16 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D318" t="n">
-        <v>-0.1612210892630528</v>
+        <v>0.7737159440364121</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MediaTek MT6739</t>
+          <t>MediaTek MT6572</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5810,16 +5608,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D319" t="n">
-        <v>-1.242493131028885</v>
+        <v>-1.422506048930607</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Spreadtrum SC6531F</t>
+          <t>Apple A15 Bionic</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5828,16 +5626,16 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D320" t="n">
-        <v>-0.8444655972497365</v>
+        <v>-0.3527303806865493</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Snapdragon 678</t>
+          <t>MediaTek MT6739</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5846,16 +5644,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="D321" t="n">
-        <v>0.9434792398758063</v>
+        <v>-1.582454118095155</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MediaTek Helio G96</t>
+          <t>Spreadtrum SC6531F</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5866,14 +5664,12 @@
       <c r="C322" t="n">
         <v>2</v>
       </c>
-      <c r="D322" t="n">
-        <v>-0.8208900882376023</v>
-      </c>
+      <c r="D322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Snapdragon 720G</t>
+          <t>Snapdragon 678</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5882,16 +5678,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D323" t="n">
-        <v>0.6258673894530113</v>
+        <v>0.4509799868884558</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Exynos 1280 (5 nm)</t>
+          <t>MediaTek Helio G96</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5900,16 +5696,14 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>18</v>
-      </c>
-      <c r="D324" t="n">
-        <v>1.389214253995005</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Exynos 1280</t>
+          <t>Snapdragon 720G</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5918,14 +5712,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
-      </c>
-      <c r="D325" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.2582263378671202</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Qualcomm Snapdragon 480+ 5G (8 nm)</t>
+          <t>Exynos 1280 (5 nm)</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5934,16 +5730,16 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.9822930919465523</v>
+        <v>1.364185233067595</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MediaTek MT6853 Dimensity 700</t>
+          <t>Exynos 1280</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5952,16 +5748,14 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>7</v>
-      </c>
-      <c r="D327" t="n">
-        <v>-1.209342542882497</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MediaTek Helio G35</t>
+          <t>Qualcomm Snapdragon 480+ 5G (8 nm)</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5970,16 +5764,14 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>16</v>
-      </c>
-      <c r="D328" t="n">
-        <v>-0.5261189868654084</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Snapdragon 660</t>
+          <t>MediaTek MT6853 Dimensity 700</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5988,16 +5780,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D329" t="n">
-        <v>0.5317440946022476</v>
+        <v>-1.679061138833754</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 700 (7 nm)</t>
+          <t>MediaTek Helio G35</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -6006,16 +5798,16 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.8589782274362662</v>
+        <v>-0.6431871243995987</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Unisoc SC9863A</t>
+          <t>Snapdragon 660</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6024,16 +5816,16 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D331" t="n">
-        <v>0.3966922673741656</v>
+        <v>0.2423271242533361</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Mediatek Helio P22 (12 nm)</t>
+          <t>MediaTek Dimensity 700 (7 nm)</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -6042,16 +5834,14 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>8</v>
-      </c>
-      <c r="D332" t="n">
-        <v>0.1616503943151544</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 700</t>
+          <t>Unisoc SC9863A</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -6060,16 +5850,16 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.1221029539286767</v>
+        <v>-0.02233769543279829</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>MediaTek Helio P60</t>
+          <t>Mediatek Helio P22 (12 nm)</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6078,16 +5868,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.252313236331378</v>
+        <v>0.1817740740653435</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Exynos 850 (8nm)</t>
+          <t>MediaTek Dimensity 700</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -6096,14 +5886,16 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
-      </c>
-      <c r="D335" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D335" t="n">
+        <v>-0.4439082130444738</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Qualcomm QM215</t>
+          <t>MediaTek Helio P60</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -6112,16 +5904,14 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>54</v>
-      </c>
-      <c r="D336" t="n">
-        <v>-1.206244826934914</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MediaTek MT6771T Helio P70</t>
+          <t>Exynos 850 (8nm)</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -6130,16 +5920,14 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>2</v>
-      </c>
-      <c r="D337" t="n">
-        <v>-0.8235914714432825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Snapdragon 662</t>
+          <t>Qualcomm QM215</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -6148,16 +5936,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D338" t="n">
-        <v>0.867400755988177</v>
+        <v>-1.381931177336125</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Snapdragon 695</t>
+          <t>MediaTek MT6771T Helio P70</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -6168,14 +5956,12 @@
       <c r="C339" t="n">
         <v>2</v>
       </c>
-      <c r="D339" t="n">
-        <v>-0.9602105584970926</v>
-      </c>
+      <c r="D339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 1100</t>
+          <t>Snapdragon 662</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6184,16 +5970,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.2922324760313558</v>
+        <v>0.4743145868639571</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Snapdragon 888 5G</t>
+          <t>Snapdragon 695</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6202,16 +5988,14 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>5</v>
-      </c>
-      <c r="D341" t="n">
-        <v>-0.381728962252007</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Snapdragon 860</t>
+          <t>MediaTek Dimensity 1100</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -6220,16 +6004,16 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D342" t="n">
-        <v>0.5394729678450456</v>
+        <v>-0.6224650945762644</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MediaTek MT6761D Helio A20</t>
+          <t>Snapdragon 888 5G</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -6238,16 +6022,16 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D343" t="n">
-        <v>-1.034241469661773</v>
+        <v>-0.716394785849762</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Snapdragon 480 Plus</t>
+          <t>Snapdragon 860</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -6256,14 +6040,16 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>0</v>
-      </c>
-      <c r="D344" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.273280154939602</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Apple A12 Bionic</t>
+          <t>MediaTek MT6761D Helio A20</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6272,16 +6058,14 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>10</v>
-      </c>
-      <c r="D345" t="n">
-        <v>0.479456282835934</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>MediaTek MT6261D</t>
+          <t>Snapdragon 480 Plus</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6290,16 +6074,14 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>7</v>
-      </c>
-      <c r="D346" t="n">
-        <v>-0.9348983773340188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Unisoc T700</t>
+          <t>Apple A12 Bionic</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6308,16 +6090,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D347" t="n">
-        <v>0.4011757538060337</v>
+        <v>-0.03417119340838333</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Exynos 9611</t>
+          <t>MediaTek Dimensity 800</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6326,16 +6108,14 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>27</v>
-      </c>
-      <c r="D348" t="n">
-        <v>-0.1619565142621253</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Snapdragon 780G</t>
+          <t>MediaTek MT6261D</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6344,16 +6124,16 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D349" t="n">
-        <v>0.125485084528614</v>
+        <v>-1.299795536843461</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Snapdragon 750G</t>
+          <t>Unisoc T700</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6362,16 +6142,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D350" t="n">
-        <v>-1.035425962572607</v>
+        <v>-0.341042706927531</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>MediaTek MT6779 Helio P90</t>
+          <t>Exynos 9611</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6380,16 +6160,16 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D351" t="n">
-        <v>-1.400068206760639</v>
+        <v>-0.2948573279365773</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MediaTek MT6765 Helio P35</t>
+          <t>Snapdragon 780G</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -6398,16 +6178,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4062963839185792</v>
+        <v>-0.2209489493758281</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Snapdragon 855+</t>
+          <t>Snapdragon 750G</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -6416,16 +6196,14 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>7</v>
-      </c>
-      <c r="D353" t="n">
-        <v>0.08633637477591027</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>MediaTek MT6580</t>
+          <t>MediaTek MT6779 Helio P90</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6436,14 +6214,12 @@
       <c r="C354" t="n">
         <v>1</v>
       </c>
-      <c r="D354" t="n">
-        <v>-1.462267694446579</v>
-      </c>
+      <c r="D354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Snapdragon 870 5G (7 nm)</t>
+          <t>MediaTek MT6765 Helio P35</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6452,14 +6228,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0</v>
-      </c>
-      <c r="D355" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.1587779778186977</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>SPRD 6531E</t>
+          <t>Snapdragon 855+</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -6468,16 +6246,16 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D356" t="n">
-        <v>-1.207662155845699</v>
+        <v>-0.2251438500927667</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MediaTek MT6762V/WD</t>
+          <t>MediaTek MT6580</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -6486,16 +6264,14 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
-      </c>
-      <c r="D357" t="n">
-        <v>-1.029009181973742</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Snapdragon 630</t>
+          <t>Snapdragon 870 5G (7 nm)</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6504,16 +6280,14 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>4</v>
-      </c>
-      <c r="D358" t="n">
-        <v>-0.8180390744604733</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Qualcomm Snapdragon 680 4G (6 nm)</t>
+          <t>SPRD 6531E</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6522,14 +6296,14 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Exynos 990</t>
+          <t>MediaTek MT6762V/WD</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6538,16 +6312,14 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>36</v>
-      </c>
-      <c r="D360" t="n">
-        <v>0.7643800075340651</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Mediatek MT6765V/CB Helio G37</t>
+          <t>Snapdragon 630</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6558,14 +6330,12 @@
       <c r="C361" t="n">
         <v>3</v>
       </c>
-      <c r="D361" t="n">
-        <v>-1.634482659842684</v>
-      </c>
+      <c r="D361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Snapdragon 439</t>
+          <t>Qualcomm Snapdragon 680 4G (6 nm)</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6574,16 +6344,14 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>12</v>
-      </c>
-      <c r="D362" t="n">
-        <v>-0.1508013928820409</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MediaTek Helio G90T</t>
+          <t>Exynos 990</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6592,16 +6360,16 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D363" t="n">
-        <v>0.7794228782348377</v>
+        <v>-0.02645130001888976</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Spreadtrum SC6531E</t>
+          <t>Mediatek MT6765V/CB Helio G37</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6610,16 +6378,14 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>7</v>
-      </c>
-      <c r="D364" t="n">
-        <v>-1.627555695827631</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Exynos 7884</t>
+          <t>Snapdragon 439</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6628,16 +6394,16 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D365" t="n">
-        <v>0.6040191134860484</v>
+        <v>-0.7198509503266634</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Snapdragon 665</t>
+          <t>MediaTek Helio G90T</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6646,16 +6412,16 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D366" t="n">
-        <v>0.6457562072486224</v>
+        <v>0.6738058315055587</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MediaTek MT6762V Helio P22</t>
+          <t>Spreadtrum SC6531E</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6664,16 +6430,16 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D367" t="n">
-        <v>-1.142797801541324</v>
+        <v>-2.469156379249451</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Snapdragon 632</t>
+          <t>Exynos 7884</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6682,16 +6448,16 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.4649264343462949</v>
+        <v>0.3418481479075204</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MediaTek MT6771 Helio P60</t>
+          <t>Snapdragon 665</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6700,14 +6466,16 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>0</v>
-      </c>
-      <c r="D369" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.304621851926372</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MediaTek MT6261</t>
+          <t>MediaTek MT6762V Helio P22</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6716,14 +6484,14 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Snapdragon 865+</t>
+          <t>Snapdragon 632</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6732,16 +6500,16 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.8150764462713188</v>
+        <v>-0.8049589834988531</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Snapdragon 865</t>
+          <t>MediaTek MT6771 Helio P60</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6750,16 +6518,14 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
-      </c>
-      <c r="D372" t="n">
-        <v>-1.248918719418278</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SC6531E</t>
+          <t>MediaTek MT6261</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6775,7 +6541,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Apple A10 Fusion</t>
+          <t>Snapdragon 865+</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6784,16 +6550,16 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D374" t="n">
-        <v>0.8480822861874876</v>
+        <v>-1.270150246821138</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Snapdragon 765G</t>
+          <t>Snapdragon 865</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6802,14 +6568,14 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Snapdragon 730</t>
+          <t>SC6531E</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6818,16 +6584,14 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>15</v>
-      </c>
-      <c r="D376" t="n">
-        <v>0.2391772783727691</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Google Tensor</t>
+          <t>Apple A10 Fusion</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6836,14 +6600,16 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>0</v>
-      </c>
-      <c r="D377" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.5256993168102208</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Snapdragon 710</t>
+          <t>MediaTek MT6873 Dimensity 800 5G</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6852,16 +6618,14 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>22</v>
-      </c>
-      <c r="D378" t="n">
-        <v>0.3736857592640308</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Spreadtrum SC9863 Octa-core</t>
+          <t>Snapdragon 765G</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6870,16 +6634,14 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1</v>
-      </c>
-      <c r="D379" t="n">
-        <v>-1.034063298855751</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Qualcomm Snapdragon 750G 5G (8 nm)</t>
+          <t>Snapdragon 730</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6888,14 +6650,16 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>0</v>
-      </c>
-      <c r="D380" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.1421451269067239</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Exynos 7904</t>
+          <t>Google Tensor</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6904,16 +6668,14 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>49</v>
-      </c>
-      <c r="D381" t="n">
-        <v>0.6751747246879195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Exynos 7870</t>
+          <t>Snapdragon 710</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6922,16 +6684,16 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D382" t="n">
-        <v>0.9677714287611392</v>
+        <v>-0.05054716385229292</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Exynos 7580</t>
+          <t>Spreadtrum SC9863 Octa-core</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6940,14 +6702,14 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MediaTek Helio P22</t>
+          <t>Qualcomm Snapdragon 750G 5G (8 nm)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6963,7 +6725,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 800U</t>
+          <t>Exynos 7904</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6972,16 +6734,16 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D385" t="n">
-        <v>0.3965352980348175</v>
+        <v>0.5712737821551573</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 810</t>
+          <t>Exynos 7870</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6990,14 +6752,16 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>0</v>
-      </c>
-      <c r="D386" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.5891701279712537</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>MTK6739 Quad Core</t>
+          <t>Exynos 7580</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -7006,16 +6770,14 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>2</v>
-      </c>
-      <c r="D387" t="n">
-        <v>-1.677093772402518</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Snapdragon 835</t>
+          <t>MediaTek Helio P22</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -7024,16 +6786,14 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>14</v>
-      </c>
-      <c r="D388" t="n">
-        <v>0.4104598721528976</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Exynos</t>
+          <t>MediaTek Dimensity 800U</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7042,14 +6802,16 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0</v>
-      </c>
-      <c r="D389" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D389" t="n">
+        <v>-0.1103976241190468</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Exynos 8890</t>
+          <t>MediaTek Dimensity 810</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7058,16 +6820,14 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>17</v>
-      </c>
-      <c r="D390" t="n">
-        <v>1.181211264226171</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>QM215</t>
+          <t>MTK6739 Quad Core</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -7076,16 +6836,14 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>15</v>
-      </c>
-      <c r="D391" t="n">
-        <v>-1.468619295229425</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Exynos 9610</t>
+          <t>Snapdragon 835</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7094,16 +6852,16 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D392" t="n">
-        <v>1.332256618688608</v>
+        <v>-0.1445260775904</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Apple A11 Bionic</t>
+          <t>Exynos</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -7112,16 +6870,14 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>17</v>
-      </c>
-      <c r="D393" t="n">
-        <v>1.898695716304397</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>MediaTek Helio G88</t>
+          <t>Exynos 8890</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -7130,16 +6886,16 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D394" t="n">
-        <v>0.7897914732931623</v>
+        <v>1.285154539248524</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Snapdragon 480</t>
+          <t>QM215</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -7148,14 +6904,16 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>0</v>
-      </c>
-      <c r="D395" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D395" t="n">
+        <v>-1.635233997321683</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MediaTek MT6833 Dimensity 700</t>
+          <t>Exynos 9610</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -7164,16 +6922,16 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D396" t="n">
-        <v>0.2479364225914089</v>
+        <v>1.115461872473334</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Snapdragon 675</t>
+          <t>Apple A11 Bionic</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -7182,16 +6940,16 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D397" t="n">
-        <v>0.8123980307512029</v>
+        <v>1.901216783593198</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Snapdragon 730G</t>
+          <t>MediaTek Helio G88</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -7200,16 +6958,16 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D398" t="n">
-        <v>1.269599198709288</v>
+        <v>0.5131568700672007</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Snapdragon 625</t>
+          <t>Snapdragon 480</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -7218,16 +6976,14 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>17</v>
-      </c>
-      <c r="D399" t="n">
-        <v>0.1703359366940946</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MediaTek MT6785 Helio G95</t>
+          <t>Helio G35 Octa core</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7236,16 +6992,14 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>1</v>
-      </c>
-      <c r="D400" t="n">
-        <v>-1.034251060626751</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>MediaTek MT6762V/WD Helio A25</t>
+          <t>MediaTek MT6833 Dimensity 700</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -7254,16 +7008,16 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D401" t="n">
-        <v>-0.8205471184591761</v>
+        <v>-0.05553895003368819</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Snapdragon 690</t>
+          <t>Snapdragon 675</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7272,14 +7026,16 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>0</v>
-      </c>
-      <c r="D402" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.6061756755481411</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Snapdragon 670</t>
+          <t>Snapdragon 730G</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7288,14 +7044,16 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>0</v>
-      </c>
-      <c r="D403" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.8469456445564675</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MediaTek MT6771V/CT Helio P70</t>
+          <t>Snapdragon 625</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7304,14 +7062,16 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>0</v>
-      </c>
-      <c r="D404" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.04988789386126499</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MediaTek MT6785T Helio G90T</t>
+          <t>MediaTek MT6785 Helio G95</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7320,14 +7080,14 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Apple A9</t>
+          <t>MediaTek MT6762V/WD Helio A25</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7336,16 +7096,14 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>25</v>
-      </c>
-      <c r="D406" t="n">
-        <v>2.081545923738744</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Exynos 5430</t>
+          <t>Snapdragon 690</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7354,16 +7112,14 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>6</v>
-      </c>
-      <c r="D407" t="n">
-        <v>-0.2077054416674777</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Snapdragon 210</t>
+          <t>Snapdragon 670</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7372,16 +7128,14 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>6</v>
-      </c>
-      <c r="D408" t="n">
-        <v>-1.952945367359962</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Exynos 7570</t>
+          <t>MediaTek MT6771V/CT Helio P70</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -7390,16 +7144,14 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>37</v>
-      </c>
-      <c r="D409" t="n">
-        <v>0.8716539709248444</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Snapdragon 821</t>
+          <t>MediaTek MT6785T Helio G90T</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7415,7 +7167,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Exynos 7880</t>
+          <t>Apple A9</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7424,16 +7176,16 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D411" t="n">
-        <v>1.557494950653346</v>
+        <v>2.069310725511989</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MediaTek MT6762 Helio P22</t>
+          <t>Exynos 5430</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -7442,16 +7194,16 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="D412" t="n">
-        <v>0.8222203721365032</v>
+        <v>-0.533751016768913</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Exynos 9820</t>
+          <t>Snapdragon 210</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7460,14 +7212,16 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>0</v>
-      </c>
-      <c r="D413" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-2.073660131058547</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Unisoc T606</t>
+          <t>Exynos 7570</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -7476,16 +7230,16 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D414" t="n">
-        <v>-0.03502942333131744</v>
+        <v>0.8041805968280867</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Exynos 9810</t>
+          <t>Snapdragon 821</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7501,7 +7255,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>MediaTek MT6737T</t>
+          <t>Exynos 7880</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7510,16 +7264,16 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="D416" t="n">
-        <v>0.2334544387943653</v>
+        <v>1.362815566516275</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Exynos 7420</t>
+          <t>MediaTek MT6762 Helio P22</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -7528,16 +7282,16 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D417" t="n">
-        <v>1.270636389096599</v>
+        <v>0.4660066095703494</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MediaTek Dimensity 920 5G</t>
+          <t>Exynos 9820</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -7553,7 +7307,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Snapdragon 200</t>
+          <t>Exynos 2200</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7562,16 +7316,14 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>4</v>
-      </c>
-      <c r="D419" t="n">
-        <v>-0.8977640678017789</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Exynos 7885</t>
+          <t>Unisoc T606</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -7580,16 +7332,16 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D420" t="n">
-        <v>0.5760970846477284</v>
+        <v>-0.4342488769096437</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Snapdragon 636</t>
+          <t>Exynos 9810</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7598,16 +7350,14 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>15</v>
-      </c>
-      <c r="D421" t="n">
-        <v>0.7299895903410186</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Snapdragon 410</t>
+          <t>MediaTek MT6737T</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -7616,16 +7366,16 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D422" t="n">
-        <v>0.5369122839636611</v>
+        <v>-0.07073829834922281</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MediaTek MT6757 Helio P25</t>
+          <t>Exynos 7420</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7634,16 +7384,16 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D423" t="n">
-        <v>-1.457721003687449</v>
+        <v>1.206811038809431</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Snapdragon 425</t>
+          <t>MediaTek Dimensity 920 5G</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -7652,16 +7402,14 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>25</v>
-      </c>
-      <c r="D424" t="n">
-        <v>1.124514571515172</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Snapdragon 820</t>
+          <t>Snapdragon 200</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7670,14 +7418,14 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>HiSilicon Kirin 980</t>
+          <t>Exynos 7885</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -7686,16 +7434,16 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D426" t="n">
-        <v>-1.158783379305247</v>
+        <v>0.3502492554320906</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Apple A7</t>
+          <t>Snapdragon 636</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7704,16 +7452,16 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D427" t="n">
-        <v>-0.4133840162088378</v>
+        <v>0.4517782842411451</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MediaTek MT6753</t>
+          <t>Snapdragon 410</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7722,14 +7470,16 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>0</v>
-      </c>
-      <c r="D428" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0.1963166950330705</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Snapdragon 212</t>
+          <t>MediaTek MT6757 Helio P25</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -7738,16 +7488,14 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>20</v>
-      </c>
-      <c r="D429" t="n">
-        <v>-0.8899885908416306</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Snapdragon 765 5G</t>
+          <t>Snapdragon 425</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7756,14 +7504,16 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>0</v>
-      </c>
-      <c r="D430" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0.7772996586471231</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Exynos 5</t>
+          <t>Snapdragon 820</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7772,16 +7522,14 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>18</v>
-      </c>
-      <c r="D431" t="n">
-        <v>0.3096988074018758</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Snapdragon 615</t>
+          <t>HiSilicon Kirin 980</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7790,16 +7538,14 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>27</v>
-      </c>
-      <c r="D432" t="n">
-        <v>-0.04793599446440418</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Snapdragon 450</t>
+          <t>Apple A7</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7808,16 +7554,16 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D433" t="n">
-        <v>0.1429759410029893</v>
+        <v>-1.11031360172022</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Snapdragon 215</t>
+          <t>MediaTek MT6753</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7826,16 +7572,14 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>15</v>
-      </c>
-      <c r="D434" t="n">
-        <v>-0.5819350180976898</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Exynos 8895</t>
+          <t>Snapdragon 212</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7844,16 +7588,16 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D435" t="n">
-        <v>-0.3447537249958552</v>
+        <v>-1.245250643926159</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MediaTek MT6762D</t>
+          <t>Snapdragon 765 5G</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -7869,7 +7613,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Exynos 9609</t>
+          <t>Exynos 5</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7878,16 +7622,16 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D437" t="n">
-        <v>1.269324323859499</v>
+        <v>0.4539655781696385</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MediaTek MT6276W</t>
+          <t>Snapdragon 615</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7896,14 +7640,16 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>0</v>
-      </c>
-      <c r="D438" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D438" t="n">
+        <v>-0.1919074594812049</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Exynos 3475</t>
+          <t>Snapdragon 450</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7912,16 +7658,16 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.105921989242247</v>
+        <v>-0.2073379699981509</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Snapdragon 845</t>
+          <t>Snapdragon 215</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7930,16 +7676,16 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D440" t="n">
-        <v>-1.011327918009579</v>
+        <v>-1.000637297626877</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Unisoc T610</t>
+          <t>Exynos 8895</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7948,14 +7694,16 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>0</v>
-      </c>
-      <c r="D441" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D441" t="n">
+        <v>-0.6616450313685588</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Apple A8</t>
+          <t>MediaTek MT6762D</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7964,16 +7712,14 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>8</v>
-      </c>
-      <c r="D442" t="n">
-        <v>-0.1541303442836614</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MediaTek MT6797 Helio X20</t>
+          <t>Exynos 9609</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7982,14 +7728,16 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>0</v>
-      </c>
-      <c r="D443" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0.7960942626626089</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MediaTek MT6768 Helio P65</t>
+          <t>MediaTek MT6276W</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7998,16 +7746,14 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>12</v>
-      </c>
-      <c r="D444" t="n">
-        <v>-0.372661554560004</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MediaTek MT6735</t>
+          <t>Exynos 3475</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -8016,16 +7762,16 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D445" t="n">
-        <v>-0.05565521060008791</v>
+        <v>-0.5415561575927619</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>HiSilicon Kirin 650</t>
+          <t>Snapdragon 845</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -8034,16 +7780,14 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>14</v>
-      </c>
-      <c r="D446" t="n">
-        <v>0.7224398823771391</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MediaTek MT6737M</t>
+          <t>Unisoc T610</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -8052,16 +7796,14 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>19</v>
-      </c>
-      <c r="D447" t="n">
-        <v>-1.087590416777238</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MediaTek Helio P35</t>
+          <t>Apple A8</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -8070,191 +7812,199 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D448" t="n">
-        <v>-2.331617567368773</v>
+        <v>-0.4775220789667913</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
+          <t>MediaTek MT6797 Helio X20</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>MediaTek MT6768 Helio P65</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>12</v>
+      </c>
+      <c r="D450" t="n">
+        <v>-0.8641045117408319</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>MediaTek MT6735</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>30</v>
+      </c>
+      <c r="D451" t="n">
+        <v>-0.3540121647694999</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>HiSilicon Kirin 650</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>16</v>
+      </c>
+      <c r="D452" t="n">
+        <v>0.5657344794345803</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>MediaTek MT6737M</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>18</v>
+      </c>
+      <c r="D453" t="n">
+        <v>-1.67994371158567</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>MediaTek Helio P35</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Modelo del procesador</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>18</v>
+      </c>
+      <c r="D454" t="n">
+        <v>-3.657351573058872</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
           <t>HiSilicon Kirin 659</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Modelo del procesador</t>
-        </is>
-      </c>
-      <c r="C449" t="n">
-        <v>21</v>
-      </c>
-      <c r="D449" t="n">
-        <v>0.9536107736676577</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="n">
-        <v>8</v>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="C450" t="n">
-        <v>1791</v>
-      </c>
-      <c r="D450" t="n">
-        <v>1.148065558463826</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="n">
-        <v>6</v>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="C451" t="n">
-        <v>69</v>
-      </c>
-      <c r="D451" t="n">
-        <v>-0.6810799889193115</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="n">
-        <v>4</v>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="C452" t="n">
-        <v>469</v>
-      </c>
-      <c r="D452" t="n">
-        <v>-0.4669855695445139</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="n">
-        <v>10</v>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="C453" t="n">
-        <v>0</v>
-      </c>
-      <c r="D453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Velocidad del procesador</t>
-        </is>
-      </c>
-      <c r="C454" t="n">
-        <v>461</v>
-      </c>
-      <c r="D454" t="n">
-        <v>1.02651830950803</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="n">
-        <v>2.1</v>
-      </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Velocidad del procesador</t>
+          <t>Modelo del procesador</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D455" t="n">
-        <v>-0.3571525890212093</v>
+        <v>0.8008500246092143</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1.65</v>
+        <v>8</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Velocidad del procesador</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>526</v>
+        <v>1807</v>
       </c>
       <c r="D456" t="n">
-        <v>0.5061433858906318</v>
+        <v>0.7071067811865476</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>3.16</v>
+        <v>6</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Velocidad del procesador</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>62</v>
-      </c>
-      <c r="D457" t="n">
-        <v>1.351704542321289</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Velocidad del procesador</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>112</v>
+        <v>482</v>
       </c>
       <c r="D458" t="n">
-        <v>0.2324163696517773</v>
+        <v>-0.7071067811865476</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Velocidad del procesador</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>54</v>
-      </c>
-      <c r="D459" t="n">
-        <v>-0.9716682261183311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -8262,15 +8012,15 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="D460" t="n">
-        <v>0.9936886379598753</v>
+        <v>0.9656630980323013</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -8278,15 +8028,15 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="D461" t="n">
-        <v>1.522093580894591</v>
+        <v>-0.357026307418996</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2.575</v>
+        <v>1.65</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -8294,15 +8044,15 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>43</v>
+        <v>542</v>
       </c>
       <c r="D462" t="n">
-        <v>-0.8418353862377537</v>
+        <v>0.4420162789762279</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -8310,15 +8060,15 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>319</v>
+        <v>60</v>
       </c>
       <c r="D463" t="n">
-        <v>-0.5816143273691378</v>
+        <v>1.458872438098822</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -8326,15 +8076,15 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="D464" t="n">
-        <v>-1.280543777806229</v>
+        <v>0.1985531825603465</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -8342,15 +8092,15 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D465" t="n">
-        <v>-0.3168027342016287</v>
+        <v>-1.002978979616158</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>2.345</v>
+        <v>2.25</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -8358,42 +8108,136 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>51</v>
+        <v>393</v>
       </c>
       <c r="D466" t="n">
-        <v>-1.282947785471903</v>
+        <v>0.8849691085031129</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Con flash en la cámara frontal</t>
+          <t>Velocidad del procesador</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>1446</v>
+        <v>48</v>
       </c>
       <c r="D467" t="n">
-        <v>-0.7071067811865493</v>
+        <v>1.181458845672352</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>39</v>
+      </c>
+      <c r="D468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>326</v>
+      </c>
+      <c r="D469" t="n">
+        <v>-0.5009513568335212</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>54</v>
+      </c>
+      <c r="D470" t="n">
+        <v>-1.365684984025429</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>81</v>
+      </c>
+      <c r="D471" t="n">
+        <v>-0.4720390253779934</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Velocidad del procesador</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>53</v>
+      </c>
+      <c r="D472" t="n">
+        <v>-1.432852298571064</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>0</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Con flash en la cámara frontal</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>1427</v>
+      </c>
+      <c r="D473" t="n">
+        <v>-0.7071067811865475</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
         <v>1</v>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>Con flash en la cámara frontal</t>
         </is>
       </c>
-      <c r="C468" t="n">
-        <v>472</v>
-      </c>
-      <c r="D468" t="n">
-        <v>0.7071067811865458</v>
+      <c r="C474" t="n">
+        <v>465</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0.7071067811865475</v>
       </c>
     </row>
   </sheetData>
